--- a/artfynd/A 41053-2024 artfynd.xlsx
+++ b/artfynd/A 41053-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>173848</v>
       </c>
       <c r="B2" t="n">
-        <v>93021</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96313</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +700,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(With.) Myrin</t>
+          <t>(L. ex Dicks.) Myrin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521611.9225520659</v>
+        <v>521612</v>
       </c>
       <c r="R2" t="n">
-        <v>6242155.721412084</v>
+        <v>6242156</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,19 +754,9 @@
           <t>1999-09-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1999-09-30</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
